--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q80"/>
+  <dimension ref="A1:Q89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7198,6 +7198,771 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>03/29/2025</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1.500%</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1.500%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>78752</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>709</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>5250114</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>8.100%</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>-5.100%</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>GMMX-134404218</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>11/08/2025</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.800%</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2.800%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>186601</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>1642</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>6547735</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>21.600%</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>1.800%</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>GMMX-134663952</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>06/23/2025</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Encompass Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>3761524</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>GMMX-134490929</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>10/13/2025</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-14.791%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>-2798</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>18919</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>11.100%</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>-23.800%</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>GMMX-134694672</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2025-10-03</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>02/15/2026</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>91072</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>310820277</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>LBPM-134762479</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>LBPM-134450061</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>49.300%</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>36.000%</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>6297755</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>17719</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>17506322</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>75.300%</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>LBPM-134412448</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>17.100%</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>13.500%</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>28040694</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>54702</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>207965553</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>72.400%</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-33.200%</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>LBPM-134412448</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>04/18/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>12.800%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>5.200%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>9888509</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>45640</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>191265327</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>66.600%</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-28.800%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>LBPM-134870677</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:Q93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1799,14 +1799,19 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>23.200%</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>177509947</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1814,17 +1819,17 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1256594719</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>50.400%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.800%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1834,7 +1839,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SFMA-134604280</t>
+          <t>SFMA-134522369</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1844,12 +1849,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1861,7 +1866,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1876,35 +1881,30 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>10.300%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>453710</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>5717</v>
+        <v>545361</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4557304</t>
+          <t>1256594719</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SFMA-134452674</t>
+          <t>SFMA-134604280</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1929,12 +1929,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1946,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1961,40 +1961,40 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>9.800%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11393108</t>
+          <t>453710</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>60097</v>
+        <v>5717</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>116259930</t>
+          <t>4557304</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>38.000%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SFMA-134620253</t>
+          <t>SFMA-134452674</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2051,35 +2051,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>9.800%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2433030</t>
+          <t>11393108</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>25748</v>
+        <v>60097</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19304787</t>
+          <t>116259930</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>14.900%</t>
+          <t>38.000%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-8.300%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SFMA-134620275</t>
+          <t>SFMA-134620253</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2116,55 +2116,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2433030</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2036</v>
+        <v>25748</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5840869</t>
+          <t>19304787</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>14.900%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>SFMA-134620275</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2184,12 +2184,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2235,21 +2235,21 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>91970</v>
+        <v>2036</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>202911983</t>
+          <t>5840869</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-24.400%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2320,21 +2320,21 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>10392</v>
+        <v>91970</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23811967</t>
+          <t>202911983</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>32.400%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-33.500%</t>
+          <t>-24.400%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2405,21 +2405,21 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3767</v>
+        <v>10392</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>9904386</t>
+          <t>23811967</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>17.800%</t>
+          <t>32.400%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-26.000%</t>
+          <t>-33.500%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2490,21 +2490,21 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>13868</v>
+        <v>3767</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>33792307</t>
+          <t>9904386</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>42.900%</t>
+          <t>17.800%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-23.500%</t>
+          <t>-26.000%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2575,21 +2575,21 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>92440</v>
+        <v>13868</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>231003997</t>
+          <t>33792307</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>50.200%</t>
+          <t>42.900%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-30.300%</t>
+          <t>-23.500%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2660,21 +2660,21 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2112</v>
+        <v>92440</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>231003997</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>7.420%</t>
+          <t>50.200%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-10.170%</t>
+          <t>-30.300%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GECC-134532692</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2745,21 +2745,21 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>95787</v>
+        <v>2112</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>30.380%</t>
+          <t>7.420%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-23.560%</t>
+          <t>-10.170%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>10839</v>
+        <v>95787</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8.510%</t>
+          <t>30.380%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-11.790%</t>
+          <t>-23.560%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3979</v>
+        <v>10839</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>7.040%</t>
+          <t>8.510%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3000,21 +3000,21 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>13867</v>
+        <v>3979</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>18.970%</t>
+          <t>7.040%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-14.320%</t>
+          <t>-11.790%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3085,11 +3085,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>93994</v>
+        <v>13867</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3170,21 +3170,21 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2036</v>
+        <v>93994</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>7.530%</t>
+          <t>18.970%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-8.420%</t>
+          <t>-14.320%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3194,7 +3194,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GECC-134788014</t>
+          <t>GECC-134532692</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3255,21 +3255,21 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>91970</v>
+        <v>2036</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>28.970%</t>
+          <t>7.530%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-25.040%</t>
+          <t>-8.420%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3340,21 +3340,21 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>10392</v>
+        <v>91970</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>8.500%</t>
+          <t>28.970%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-11.740%</t>
+          <t>-25.040%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3425,16 +3425,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3767</v>
+        <v>10392</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6.190%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3510,21 +3510,21 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13868</v>
+        <v>3767</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>17.990%</t>
+          <t>6.190%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-13.460%</t>
+          <t>-11.740%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>92440</v>
+        <v>13868</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>21.180%</t>
+          <t>17.990%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>-13.460%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3666,35 +3666,35 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-66805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>596</v>
+        <v>92440</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1590594</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>21.180%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-14.930%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3704,7 +3704,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134788014</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3736,7 +3736,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3751,35 +3751,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-7.390%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-22357214</t>
+          <t>-66805</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>345517</v>
+        <v>596</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>745240469</t>
+          <t>1590594</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25.060%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-15.970%</t>
+          <t>-14.930%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3836,35 +3836,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-7.390%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-6.100%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-18329542</t>
+          <t>-22357214</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>117383</v>
+        <v>345517</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>300484287</t>
+          <t>745240469</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22.510%</t>
+          <t>25.060%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-25.160%</t>
+          <t>-15.970%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-6.100%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-28973</t>
+          <t>-18329542</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>226</v>
+        <v>117383</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>658471</t>
+          <t>300484287</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>8.180%</t>
+          <t>22.510%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-12.990%</t>
+          <t>-25.160%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4011,30 +4011,30 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-13851</t>
+          <t>-28973</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>658471</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8.720%</t>
+          <t>8.180%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-9.440%</t>
+          <t>-12.990%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4091,35 +4091,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-116057</t>
+          <t>-13851</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>583</v>
+        <v>218</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>1589822</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>-2.210%</t>
+          <t>8.720%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-9.680%</t>
+          <t>-9.440%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4181,30 +4181,30 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-22756464</t>
+          <t>-116057</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>120629</v>
+        <v>583</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>334653880</t>
+          <t>1589822</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-1.290%</t>
+          <t>-2.210%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-10.750%</t>
+          <t>-9.680%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4266,30 +4266,30 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-7.200%</t>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-48359</t>
+          <t>-22756464</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>225</v>
+        <v>120629</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>671657</t>
+          <t>334653880</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-2.120%</t>
+          <t>-1.290%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-8.890%</t>
+          <t>-10.750%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4351,30 +4351,30 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-7.200%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-35656</t>
+          <t>-48359</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-2.760%</t>
+          <t>-2.120%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-9.790%</t>
+          <t>-8.890%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4431,35 +4431,35 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-7.050%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-4.800%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-35046584</t>
+          <t>-35656</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>354385</v>
+        <v>214</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>730137175</t>
+          <t>488445</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>-2.760%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-8.560%</t>
+          <t>-9.790%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4496,55 +4496,55 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>-7.050%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>-4.800%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2774560</t>
+          <t>-35046584</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>8132</v>
+        <v>354385</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>31174837</t>
+          <t>730137175</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>7.100%</t>
+          <t>-8.560%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>ALSE-134603438</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>06/16/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4591,45 +4591,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2774560</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>8132</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>454172309</t>
+          <t>31174837</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.100%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>ALSE-134493741</t>
+          <t>ALSE-134603438</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>06/16/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4700,11 +4700,11 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>143346</v>
+        <v>0</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>523575197</t>
+          <t>454172309</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>ALSE-134681972</t>
+          <t>ALSE-134493741</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>06/07/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4766,35 +4766,35 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>15.800%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>722526</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8983</v>
+        <v>143346</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4596808</t>
+          <t>523575197</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ALSE-134493023</t>
+          <t>ALSE-134681972</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4819,12 +4819,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4836,55 +4836,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>06/07/2025</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>152460</t>
+          <t>722526</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>2321</v>
+        <v>8983</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2089620</t>
+          <t>4596808</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ALSE-134755310</t>
+          <t>ALSE-134493023</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4936,40 +4936,40 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>427475</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1706</v>
+        <v>2321</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6576532</t>
+          <t>2089620</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ALSE-134604451</t>
+          <t>ALSE-134755310</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5016,45 +5016,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-105052</t>
+          <t>427475</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>3244</v>
+        <v>1706</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>15007464</t>
+          <t>6576532</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-1.500%</t>
+          <t>5.400%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ALSE-134681921</t>
+          <t>ALSE-134604451</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5091,55 +5091,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2970856</t>
+          <t>-105052</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>7645</v>
+        <v>3244</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>24757133</t>
+          <t>15007464</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>12.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-1.500%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ALSE-134604433</t>
+          <t>ALSE-134681921</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5159,12 +5159,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -5186,45 +5186,45 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-1382427</t>
+          <t>2970856</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>9583</v>
+        <v>7645</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>32149469</t>
+          <t>24757133</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.400%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ALSE-134679258</t>
+          <t>ALSE-134604433</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5279,32 +5279,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-845422</t>
+          <t>-1382427</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>14339</v>
+        <v>9583</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>22849234</t>
+          <t>32149469</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-25.800%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5314,7 +5319,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>ALSE-134660932</t>
+          <t>ALSE-134679258</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5324,12 +5329,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5341,7 +5346,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5351,45 +5356,40 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-845422</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>11414</v>
+        <v>14339</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1590113</t>
+          <t>22849234</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>-25.800%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>ALSE-134752063</t>
+          <t>ALSE-134660932</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134752063/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>05/13/2026</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5441,40 +5441,40 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>407265</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>3705</v>
+        <v>11414</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>14545188</t>
+          <t>1590113</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-1.300%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ALSE-134604410</t>
+          <t>ALSE-134752063</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5494,12 +5494,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134752063/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5521,45 +5521,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-7.700%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-1101681</t>
+          <t>407265</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>5292</v>
+        <v>3705</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>19327737</t>
+          <t>14545188</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>ALSE-134679055</t>
+          <t>ALSE-134604410</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5596,55 +5596,55 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-7.700%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>681134</t>
+          <t>-1101681</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>18880</v>
+        <v>5292</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19459174</t>
+          <t>19327737</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>-12.700%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>ALSE-134749670</t>
+          <t>ALSE-134679055</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5681,7 +5681,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5696,40 +5696,40 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>72695887</t>
+          <t>681134</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>143688</v>
+        <v>18880</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>457206835</t>
+          <t>19459174</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>30.000%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5739,7 +5739,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>ALSE-134603603</t>
+          <t>ALSE-134749670</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5766,55 +5766,55 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72695887</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>143688</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>31819480</t>
+          <t>457206835</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>30.000%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>ALSE-134629407</t>
+          <t>ALSE-134603603</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5834,12 +5834,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5856,7 +5856,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>19152153</t>
+          <t>31819480</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>13832315</t>
+          <t>19152153</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -6021,55 +6021,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>28.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>5955691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>15472</v>
+        <v>0</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>45118871</t>
+          <t>13832315</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6079,7 +6079,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>TRVD-G134450451</t>
+          <t>ALSE-134629407</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6089,12 +6089,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6131,30 +6131,30 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>14.500%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>244055</t>
+          <t>5955691</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>584</v>
+        <v>15472</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1683140</t>
+          <t>45118871</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6191,12 +6191,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>03/14/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6211,35 +6211,35 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>28.800%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>14.500%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>29899633</t>
+          <t>244055</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>105836</v>
+        <v>584</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>302016491</t>
+          <t>1683140</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-14.800%</t>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>TRVD-G134420284</t>
+          <t>TRVD-G134450451</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>11/16/2025</t>
+          <t>03/14/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6294,32 +6294,37 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20.700%</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29899633</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>100997</v>
+        <v>105836</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>334013501</t>
+          <t>302016491</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.400%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.800%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6329,7 +6334,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>TRVD-G134688466</t>
+          <t>TRVD-G134420284</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6339,12 +6344,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6356,12 +6361,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6374,37 +6379,32 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>15.400%</t>
-        </is>
-      </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.390%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>515</v>
+        <v>100997</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>3885888</t>
+          <t>334013501</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>8.130%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>2.760%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>LBPM-134814588</t>
+          <t>TRVD-G134688466</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6424,12 +6424,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>08/17/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6459,37 +6459,32 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>15.400%</t>
-        </is>
-      </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>3.030%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>121</v>
+        <v>106478</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>520683</t>
+          <t>334013501</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>16.700%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-35.000%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6499,7 +6494,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>TRVD-G134585304</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6509,12 +6504,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6521,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6551,30 +6546,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3.040%</t>
+          <t>3.390%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>846342</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8442</v>
+        <v>515</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>27858972</t>
+          <t>3885888</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>8.130%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>2.760%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6584,7 +6579,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134814588</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6599,7 +6594,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6606,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6631,35 +6626,35 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.030%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6669,7 +6664,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6679,12 +6674,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6691,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -6716,35 +6711,35 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.040%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>846342</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>6706</v>
+        <v>8442</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>10503181</t>
+          <t>27858972</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6754,7 +6749,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6764,12 +6759,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6776,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6801,35 +6796,35 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>318742</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4146</v>
+        <v>98</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>3983816</t>
+          <t>186641</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6839,7 +6834,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6849,12 +6844,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6866,12 +6861,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LM Insurance Corporation</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6886,35 +6881,35 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>3.280%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>142004</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>747</v>
+        <v>6706</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4327846</t>
+          <t>10503181</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6924,7 +6919,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6934,12 +6929,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6951,12 +6946,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6971,35 +6966,35 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>16429</v>
+        <v>109</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>441054</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7009,7 +7004,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7019,12 +7014,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7036,27 +7031,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -7066,25 +7061,25 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>43</v>
+        <v>7015</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>23371975</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -7094,7 +7089,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7104,12 +7099,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7121,55 +7116,55 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>318742</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>30706</v>
+        <v>4146</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>3983816</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7179,7 +7174,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7189,12 +7184,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7206,45 +7201,45 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>03/29/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>LM Insurance Corporation</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>3.280%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>142004</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>709</v>
+        <v>747</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>5250114</t>
+          <t>4327846</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -7254,7 +7249,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7264,7 +7259,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>GMMX-134404218</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7274,12 +7269,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7291,12 +7286,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7311,35 +7306,35 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>1642</v>
+        <v>16429</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6547735</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7349,7 +7344,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>GMMX-134663952</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7359,12 +7354,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7371,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7391,12 +7386,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7406,25 +7401,25 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>3761524</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7434,7 +7429,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>GMMX-134490929</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7444,12 +7439,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7461,12 +7456,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7476,40 +7471,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-14.791%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-2798</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>5</v>
+        <v>30706</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-23.800%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7519,7 +7514,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GMMX-134694672</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7529,12 +7524,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7541,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>03/29/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7561,40 +7556,40 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>91072</v>
+        <v>709</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>5250114</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7604,7 +7599,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>GMMX-134404218</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7614,12 +7609,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7631,12 +7626,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7646,40 +7641,40 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1642</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6547735</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7689,7 +7684,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>GMMX-134663952</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7699,12 +7694,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7716,55 +7711,55 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>17719</v>
+        <v>0</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>3761524</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7774,7 +7769,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>GMMX-134490929</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7784,12 +7779,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7801,55 +7796,55 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>-14.791%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>-2798</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>54702</v>
+        <v>5</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>11.100%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-23.800%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7859,7 +7854,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>GMMX-134694672</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7869,12 +7864,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7886,78 +7881,418 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>02/15/2026</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>3.000%</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>91072</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>310820277</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>21.000%</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>LBPM-134762479</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>04.0001 Condominium Homeowners</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>LBPM-134450061</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2025-03-11</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>American Economy Insurance Company</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>49.300%</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>36.000%</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>6297755</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>17719</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>17506322</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>75.300%</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-15.000%</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>LBPM-134412448</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>04/14/2025</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>17.100%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>13.500%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>28040694</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>54702</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>207965553</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>72.400%</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-33.200%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>LBPM-134412448</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2025-02-14</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>04/18/2026</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>Safeco Insurance Company of America</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>12.800%</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>5.200%</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>9888509</t>
         </is>
       </c>
-      <c r="I89" t="n">
+      <c r="I93" t="n">
         <v>45640</v>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>191265327</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>66.600%</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>-28.800%</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr">
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>LBPM-134870677</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P89" t="inlineStr">
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q93"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7206,7 +7206,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LM Insurance Corporation</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -7226,30 +7226,30 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3.280%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>142004</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>747</v>
+        <v>16429</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4327846</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7286,55 +7286,55 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>16429</v>
+        <v>43</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7396,30 +7396,30 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>43</v>
+        <v>30706</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>03/29/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7471,40 +7471,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>30706</v>
+        <v>709</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>5250114</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7514,7 +7514,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>GMMX-134404218</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>03/29/2025</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -7551,45 +7551,45 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>709</v>
+        <v>1642</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>5250114</t>
+          <t>6547735</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>GMMX-134404218</t>
+          <t>GMMX-134663952</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7636,45 +7636,45 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1642</v>
+        <v>0</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>6547735</t>
+          <t>3761524</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GMMX-134663952</t>
+          <t>GMMX-134490929</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7711,12 +7711,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -7736,30 +7736,30 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.791%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2798</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>3761524</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.100%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-23.800%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GMMX-134490929</t>
+          <t>GMMX-134694672</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7811,40 +7811,40 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>-14.791%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>-2798</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>5</v>
+        <v>91072</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>310820277</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-23.800%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>GMMX-134694672</t>
+          <t>LBPM-134762479</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7864,12 +7864,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7891,17 +7891,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7915,21 +7915,21 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>91072</v>
+        <v>0</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>LBPM-134450061</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7981,40 +7981,40 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>49.300%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>36.000%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6297755</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>0</v>
+        <v>17719</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17506322</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>75.300%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8056,7 +8056,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8071,35 +8071,35 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>28040694</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>17719</v>
+        <v>54702</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>207965553</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>72.400%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-33.200%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>04/18/2026</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8156,35 +8156,35 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>12.800%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>5.200%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>9888509</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>54702</v>
+        <v>45640</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>191265327</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>66.600%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-28.800%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>LBPM-134870677</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8204,95 +8204,10 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
-        <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>04/18/2026</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Safeco Insurance Company of America</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>12.800%</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>5.200%</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>9888509</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>45640</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>191265327</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>66.600%</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>-28.800%</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>LBPM-134870677</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P93" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
         <is>
           <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q92"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,55 +511,55 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.900%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>249525</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>40568</v>
+        <v>2870</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96780298</t>
+          <t>2289687</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>26.200%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>5.500%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>SFMA-134294866</t>
+          <t>ALSE-134277277</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -579,12 +579,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134277277/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -596,55 +596,55 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.000%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>325573</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1135697</v>
+        <v>1106</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1696535022</t>
+          <t>1915852</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>35.800%</t>
+          <t>19.100%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-30.200%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SFMA-134294866</t>
+          <t>ALSE-134280614</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -664,12 +664,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134280614/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -681,55 +681,55 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0004 Tenant Homeowners</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.002%</t>
+          <t>7.400%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>371282</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>4148</v>
+        <v>30239</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1444547</t>
+          <t>4996326</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>9.100%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-9.900%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SFMA-134532992</t>
+          <t>ALSE-134280632</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -749,12 +749,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134280632/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -766,55 +766,55 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>18.300%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.005%</t>
+          <t>18.300%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-420</t>
+          <t>2922065</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>47994</v>
+        <v>18535</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7960381</t>
+          <t>15966788</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>26.800%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-13.000%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SFMA-134532992</t>
+          <t>ALSE-134335798</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2024-11-27</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134335798/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -851,12 +851,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>06/07/2025</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -866,35 +866,35 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0004 Other</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>15.800%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.005%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>722526</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4641</v>
+        <v>8983</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>1731791</t>
+          <t>4596808</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>20.000%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SFMA-134702979</t>
+          <t>ALSE-134493023</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -919,12 +919,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -936,12 +936,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>06/16/2025</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -951,35 +951,35 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.003%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>48758</v>
+        <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8319393</t>
+          <t>454172309</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SFMA-134702979</t>
+          <t>ALSE-134493741</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1021,55 +1021,55 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>8.900%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>77260</t>
+          <t>2774560</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>622</v>
+        <v>8132</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>415386</t>
+          <t>31174837</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>75.000%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.100%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>SFMA-134532940</t>
+          <t>ALSE-134603438</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1106,55 +1106,55 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13.304%</t>
+          <t>15.900%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4059986</t>
+          <t>72695887</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>82769</v>
+        <v>143688</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30516879</t>
+          <t>457206835</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>70.800%</t>
+          <t>30.000%</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-19.400%</t>
+          <t>6.100%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SFMA-134532940</t>
+          <t>ALSE-134603603</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1191,55 +1191,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.001%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>407265</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>714</v>
+        <v>3705</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>547530</t>
+          <t>14545188</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>2.900%</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>2.200%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SFMA-134702973</t>
+          <t>ALSE-134604410</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1276,55 +1276,55 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.000%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2970856</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>84036</v>
+        <v>7645</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35371108</t>
+          <t>24757133</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>12.400%</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>7.900%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SFMA-134702973</t>
+          <t>ALSE-134604433</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1361,55 +1361,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>09/04/2025</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0003 Owner Occupied Homeowners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>13.600%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-3.050%</t>
+          <t>6.500%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2489382</t>
+          <t>427475</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>35300</v>
+        <v>1706</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>81620214</t>
+          <t>6576532</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>36.200%</t>
+          <t>6.700%</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-28.600%</t>
+          <t>5.400%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SFMA-134532998</t>
+          <t>ALSE-134604451</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1471,30 +1471,30 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-4.045%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-69278198</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1152647</v>
+        <v>0</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1712624141</t>
+          <t>31819480</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>24.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-43.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SFMA-134532998</t>
+          <t>ALSE-134629407</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1514,12 +1514,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1551,35 +1551,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.959%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-5629719</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>29073</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>62836805</t>
+          <t>19152153</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-15.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SFMA-134702926</t>
+          <t>ALSE-134629407</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>09/29/2025</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1636,35 +1636,35 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-7.822%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-130056850</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1174505</v>
+        <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1662621165</t>
+          <t>13832315</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-12.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SFMA-134702926</t>
+          <t>ALSE-134629407</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-08-05</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1701,50 +1701,50 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate North American Insurance Company</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.700%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-845422</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>545361</v>
+        <v>14339</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>22849234</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.400%</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-25.800%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SFMA-134393639</t>
+          <t>ALSE-134660932</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1764,12 +1764,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1781,55 +1781,55 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Property and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>23.200%</t>
+          <t>-7.700%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>16.400%</t>
+          <t>-5.700%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>177509947</t>
+          <t>-1101681</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>545361</v>
+        <v>5292</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>19327737</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>50.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-10.800%</t>
+          <t>-12.700%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SFMA-134522369</t>
+          <t>ALSE-134679055</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1866,40 +1866,45 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Insurance Company</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-6.200%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.300%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1382427</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>545361</v>
+        <v>9583</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1256594719</t>
+          <t>32149469</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1909,7 +1914,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1919,7 +1924,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SFMA-134604280</t>
+          <t>ALSE-134679258</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1929,12 +1934,12 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -1946,55 +1951,55 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>-3.800%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>-0.700%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>453710</t>
+          <t>-105052</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>5717</v>
+        <v>3244</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>4557304</t>
+          <t>15007464</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.500%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2004,7 +2009,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SFMA-134452674</t>
+          <t>ALSE-134681921</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -2014,12 +2019,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2031,55 +2036,55 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>12/20/2025</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Fire and Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>9.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11393108</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>60097</v>
+        <v>143346</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>116259930</t>
+          <t>523575197</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>38.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2089,7 +2094,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SFMA-134620253</t>
+          <t>ALSE-134681972</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2099,12 +2104,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2116,12 +2121,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Allstate Vehicle and Property Insurance Company</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2131,40 +2136,40 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>3.500%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2433030</t>
+          <t>681134</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>25748</v>
+        <v>18880</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19304787</t>
+          <t>19459174</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>14.900%</t>
+          <t>7.000%</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>0.500%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2174,7 +2179,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SFMA-134620275</t>
+          <t>ALSE-134749670</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2184,12 +2189,12 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2201,55 +2206,55 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>01/22/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>Allstate Indemnity Company</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.300%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152460</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2036</v>
+        <v>2321</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5840869</t>
+          <t>2089620</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>20.400%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>2.000%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2259,7 +2264,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>ALSE-134755310</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2269,12 +2274,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2286,12 +2291,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>03/29/2025</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2306,35 +2311,35 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.500%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>91970</v>
+        <v>709</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>202911983</t>
+          <t>5250114</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>40.200%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-24.400%</t>
+          <t>-5.100%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2344,7 +2349,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>GMMX-134404218</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2354,12 +2359,12 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2371,12 +2376,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>06/23/2025</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2405,21 +2410,21 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>10392</v>
+        <v>0</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>23811967</t>
+          <t>3761524</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>32.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-33.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2429,7 +2434,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>GMMX-134490929</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2439,12 +2444,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2456,55 +2461,55 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>11/08/2025</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>Encompass Indemnity Company</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>186601</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3767</v>
+        <v>1642</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>9904386</t>
+          <t>6547735</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>17.800%</t>
+          <t>21.600%</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-26.000%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2514,7 +2519,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>GMMX-134663952</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2524,12 +2529,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2546,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>10/13/2025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>Encompass Insurance Company</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2566,30 +2571,30 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.791%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2798</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>13868</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>33792307</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>42.900%</t>
+          <t>11.100%</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-23.500%</t>
+          <t>-23.800%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2599,7 +2604,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>GMMX-134694672</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2609,12 +2614,12 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2626,12 +2631,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>04/02/2026</t>
+          <t>07/03/2025</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2660,21 +2665,21 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>92440</v>
+        <v>2112</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>231003997</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>50.200%</t>
+          <t>7.420%</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-30.300%</t>
+          <t>-10.170%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>GECC-134855405</t>
+          <t>GECC-134532692</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2694,12 +2699,12 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2721,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2745,21 +2750,21 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2112</v>
+        <v>95787</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>7.420%</t>
+          <t>30.380%</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-10.170%</t>
+          <t>-23.560%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2801,7 +2806,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2830,21 +2835,21 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>95787</v>
+        <v>10839</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>30.380%</t>
+          <t>8.510%</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-23.560%</t>
+          <t>-11.790%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2886,7 +2891,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2915,16 +2920,16 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>10839</v>
+        <v>3979</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>8.510%</t>
+          <t>7.040%</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2971,7 +2976,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3000,21 +3005,21 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3979</v>
+        <v>13867</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>7.040%</t>
+          <t>18.970%</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-11.790%</t>
+          <t>-14.320%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3056,7 +3061,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3085,11 +3090,11 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>13867</v>
+        <v>93994</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3136,12 +3141,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>07/03/2025</t>
+          <t>01/09/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3170,21 +3175,21 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>93994</v>
+        <v>2036</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>6572372</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18.970%</t>
+          <t>7.530%</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-14.320%</t>
+          <t>-8.420%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3194,7 +3199,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>GECC-134532692</t>
+          <t>GECC-134788014</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3204,12 +3209,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2025-05-23</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532692/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GEICO Indemnity Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3255,21 +3260,21 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2036</v>
+        <v>91970</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>6572372</t>
+          <t>254065149</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>7.530%</t>
+          <t>28.970%</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-8.420%</t>
+          <t>-25.040%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3311,7 +3316,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>GEICO Casualty Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3340,21 +3345,21 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>91970</v>
+        <v>10392</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>254065149</t>
+          <t>26803814</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>28.970%</t>
+          <t>8.500%</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-25.040%</t>
+          <t>-11.740%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3396,7 +3401,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GEICO General Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3425,16 +3430,16 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>10392</v>
+        <v>3767</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26803814</t>
+          <t>10943770</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>8.500%</t>
+          <t>6.190%</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3481,7 +3486,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Government Employees Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3510,21 +3515,21 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3767</v>
+        <v>13868</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10943770</t>
+          <t>30098648</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>6.190%</t>
+          <t>17.990%</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-11.740%</t>
+          <t>-13.460%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3566,7 +3571,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GEICO Choice Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3595,21 +3600,21 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>13868</v>
+        <v>92440</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>30098648</t>
+          <t>211526381</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>17.990%</t>
+          <t>21.180%</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-13.460%</t>
+          <t>-14.300%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3646,12 +3651,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>01/09/2026</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GEICO Secure Insurance Company</t>
+          <t>GEICO Indemnity Company</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3680,21 +3685,21 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>92440</v>
+        <v>2036</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>211526381</t>
+          <t>5840869</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>21.180%</t>
+          <t>20.400%</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3704,7 +3709,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>GECC-134788014</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3714,12 +3719,12 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134788014/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3731,12 +3736,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>GEICO Casualty Company</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3751,35 +3756,35 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-66805</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>596</v>
+        <v>91970</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1590594</t>
+          <t>202911983</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>40.200%</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-14.930%</t>
+          <t>-24.400%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3789,7 +3794,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
@@ -3799,12 +3804,12 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3821,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>GEICO General Insurance Company</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3836,35 +3841,35 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-7.390%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-22357214</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>345517</v>
+        <v>10392</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>745240469</t>
+          <t>23811967</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>25.060%</t>
+          <t>32.400%</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-15.970%</t>
+          <t>-33.500%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3874,7 +3879,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -3884,12 +3889,12 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3901,12 +3906,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Government Employees Insurance Company</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3921,35 +3926,35 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-6.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-18329542</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>117383</v>
+        <v>3767</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>300484287</t>
+          <t>9904386</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22.510%</t>
+          <t>17.800%</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-25.160%</t>
+          <t>-26.000%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -3959,7 +3964,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3969,12 +3974,12 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3991,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>GEICO Choice Insurance Company</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4006,35 +4011,35 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-28973</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>226</v>
+        <v>13868</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>658471</t>
+          <t>33792307</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>8.180%</t>
+          <t>42.900%</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-12.990%</t>
+          <t>-23.500%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -4044,7 +4049,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4054,12 +4059,12 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4071,12 +4076,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>04/02/2026</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>GEICO Secure Insurance Company</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4091,35 +4096,35 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-13851</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>218</v>
+        <v>92440</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>231003997</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>8.720%</t>
+          <t>50.200%</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-9.440%</t>
+          <t>-30.300%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -4129,7 +4134,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>GECC-134855405</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -4139,12 +4144,12 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134855405/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4156,55 +4161,55 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-116057</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>583</v>
+        <v>109</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1589822</t>
+          <t>441054</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-2.210%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-9.680%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4214,7 +4219,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4224,12 +4229,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4241,55 +4246,55 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-22756464</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>120629</v>
+        <v>7015</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>334653880</t>
+          <t>23371975</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-1.290%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-10.750%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4299,7 +4304,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4309,12 +4314,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4326,55 +4331,55 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-7.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-48359</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>225</v>
+        <v>98</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>671657</t>
+          <t>186641</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-2.120%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-8.890%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4384,7 +4389,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4394,12 +4399,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4411,55 +4416,55 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-35656</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="n">
-        <v>214</v>
+        <v>6706</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>10503181</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>-2.760%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-9.790%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4469,7 +4474,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4479,12 +4484,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4501,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4511,30 +4516,30 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-7.050%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-4.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-35046584</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>354385</v>
+        <v>43</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>730137175</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4544,7 +4549,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-8.560%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4554,7 +4559,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4564,12 +4569,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4581,55 +4586,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>8.900%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2774560</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>8132</v>
+        <v>30706</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>31174837</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>7.100%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4639,7 +4644,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>ALSE-134603438</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4649,12 +4654,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603438/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4666,55 +4671,55 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>06/16/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.030%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>454172309</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4724,7 +4729,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>ALSE-134493741</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4734,12 +4739,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493741/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4751,55 +4756,55 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.040%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>846342</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>143346</v>
+        <v>8442</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>523575197</t>
+          <t>27858972</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4809,7 +4814,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>ALSE-134681972</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4819,12 +4824,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681972/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4836,55 +4841,55 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>06/07/2025</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allstate Fire and Casualty Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>19.0004 Other</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>15.800%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>3.390%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>722526</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>8983</v>
+        <v>515</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4596808</t>
+          <t>3885888</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>20.000%</t>
+          <t>8.130%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.760%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4894,7 +4899,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>ALSE-134493023</t>
+          <t>LBPM-134814588</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4904,12 +4909,12 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134493023/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4921,12 +4926,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4936,40 +4941,40 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>7.300%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>152460</t>
+          <t>318742</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>2321</v>
+        <v>4146</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2089620</t>
+          <t>3983816</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2.000%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4979,7 +4984,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>ALSE-134755310</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4989,12 +4994,12 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134755310/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5006,12 +5011,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5021,40 +5026,40 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>6.500%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>427475</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1706</v>
+        <v>16429</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>6576532</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>6.700%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>5.400%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5064,7 +5069,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>ALSE-134604451</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5074,12 +5079,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604451/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5091,12 +5096,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5111,35 +5116,35 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-3.800%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-0.700%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-105052</t>
+          <t>-66805</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>3244</v>
+        <v>596</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>15007464</t>
+          <t>1590594</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-1.500%</t>
+          <t>-14.930%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5149,7 +5154,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ALSE-134681921</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5159,12 +5164,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134681921/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5176,55 +5181,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>-7.390%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>12.000%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2970856</t>
+          <t>-22357214</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7645</v>
+        <v>345517</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>24757133</t>
+          <t>745240469</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>12.400%</t>
+          <t>25.060%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>7.900%</t>
+          <t>-15.970%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5234,7 +5239,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ALSE-134604433</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5244,12 +5249,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604433/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5266,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5281,35 +5286,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>-6.200%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-4.300%</t>
+          <t>-6.100%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-1382427</t>
+          <t>-18329542</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9583</v>
+        <v>117383</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>32149469</t>
+          <t>300484287</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>22.510%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-14.300%</t>
+          <t>-25.160%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5319,7 +5324,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>ALSE-134679258</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5329,12 +5334,12 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679258/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5346,12 +5351,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5364,32 +5369,37 @@
           <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-14.860%</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.700%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-845422</t>
+          <t>-28973</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>14339</v>
+        <v>226</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>22849234</t>
+          <t>658471</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>3.400%</t>
+          <t>8.180%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-25.800%</t>
+          <t>-12.990%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5399,7 +5409,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>ALSE-134660932</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5409,12 +5419,12 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134660932/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5426,55 +5436,55 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>05/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Allstate North American Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>04.0004 Tenant Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-13851</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>11414</v>
+        <v>218</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1590113</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>8.720%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-1.300%</t>
+          <t>-9.440%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5484,7 +5494,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>ALSE-134752063</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5494,12 +5504,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134752063/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5511,55 +5521,55 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>407265</t>
+          <t>-116057</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3705</v>
+        <v>583</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>14545188</t>
+          <t>1589822</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2.900%</t>
+          <t>-2.210%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2.200%</t>
+          <t>-9.680%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5569,7 +5579,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>ALSE-134604410</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5579,12 +5589,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604410/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5596,12 +5606,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>12/20/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5616,35 +5626,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-7.700%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-5.700%</t>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-1101681</t>
+          <t>-22756464</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>5292</v>
+        <v>120629</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>19327737</t>
+          <t>334653880</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.290%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-12.700%</t>
+          <t>-10.750%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5654,7 +5664,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>ALSE-134679055</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5664,12 +5674,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134679055/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5681,55 +5691,55 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>01/22/2026</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3.500%</t>
+          <t>-7.200%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>681134</t>
+          <t>-48359</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>18880</v>
+        <v>225</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>19459174</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>7.000%</t>
+          <t>-2.120%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.500%</t>
+          <t>-8.890%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5739,7 +5749,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>ALSE-134749670</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5749,12 +5759,12 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134749670/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5766,55 +5776,55 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>09/04/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Allstate Vehicle and Property Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>04.0003 Owner Occupied Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>15.900%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>72695887</t>
+          <t>-35656</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>143688</v>
+        <v>214</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>457206835</t>
+          <t>488445</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>30.000%</t>
+          <t>-2.760%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>6.100%</t>
+          <t>-9.790%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5824,7 +5834,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>ALSE-134603603</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5834,12 +5844,12 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134603603/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5861,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Allstate Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5871,35 +5881,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-7.050%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.800%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-35046584</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>354385</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>31819480</t>
+          <t>730137175</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.560%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5909,7 +5919,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>ALSE-134629407</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5919,12 +5929,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5936,55 +5946,55 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Allstate Property and Casualty Insurance Company</t>
+          <t>American Economy Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>49.300%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>36.000%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6297755</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>17719</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>19152153</t>
+          <t>17506322</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>75.300%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5994,7 +6004,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>ALSE-134629407</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6004,12 +6014,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6021,55 +6031,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>09/29/2025</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Allstate Indemnity Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28040694</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>54702</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>13832315</t>
+          <t>207965553</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>72.400%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-33.200%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6079,7 +6089,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>ALSE-134629407</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6089,12 +6099,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134629407/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6106,12 +6116,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6121,40 +6131,40 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>28.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>5955691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>15472</v>
+        <v>0</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>45118871</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6164,7 +6174,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>TRVD-G134450451</t>
+          <t>LBPM-134450061</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6174,12 +6184,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6191,55 +6201,55 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>28.800%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>14.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>244055</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>584</v>
+        <v>91072</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1683140</t>
+          <t>310820277</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6249,7 +6259,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>TRVD-G134450451</t>
+          <t>LBPM-134762479</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6259,12 +6269,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6276,55 +6286,55 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>03/14/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>29899633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>105836</v>
+        <v>40568</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>302016491</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-14.800%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6334,7 +6344,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>TRVD-G134420284</t>
+          <t>SFMA-134294866</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6344,12 +6354,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6361,22 +6371,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>11/16/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6390,21 +6405,21 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>100997</v>
+        <v>1135697</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>334013501</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.800%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-30.200%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6414,7 +6429,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>TRVD-G134688466</t>
+          <t>SFMA-134294866</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6424,12 +6439,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6441,22 +6456,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>08/17/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6466,25 +6486,25 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>106478</v>
+        <v>4164</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>334013501</t>
+          <t>1513879</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>16.700%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-35.000%</t>
+          <t>-8.900%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6494,7 +6514,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>TRVD-G134585304</t>
+          <t>SFMA-134320521</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6504,12 +6524,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6521,55 +6541,55 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>3.390%</t>
+          <t>-0.004%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>515</v>
+        <v>48376</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>3885888</t>
+          <t>8064746</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>8.130%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>2.760%</t>
+          <t>-10.500%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6579,7 +6599,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>LBPM-134814588</t>
+          <t>SFMA-134320521</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6589,12 +6609,12 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6606,55 +6626,55 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>3.030%</t>
+          <t>-0.035%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>-33639</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>121</v>
+        <v>40568</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>520683</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>12.100%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-26.600%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6664,7 +6684,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>SFMA-134320536</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6674,12 +6694,12 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6691,55 +6711,55 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>3.040%</t>
+          <t>-0.013%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>846342</t>
+          <t>-213146</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>8442</v>
+        <v>1135697</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>27858972</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>-21.700%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6749,7 +6769,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>SFMA-134320536</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6759,12 +6779,12 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6776,55 +6796,55 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.001%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>98</v>
+        <v>601</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>373240</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6834,7 +6854,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>SFMA-134320543</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6844,12 +6864,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6861,27 +6881,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6891,25 +6911,25 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-122</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>6706</v>
+        <v>82673</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>10503181</t>
+          <t>30432911</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6919,7 +6939,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>SFMA-134320543</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6929,12 +6949,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6946,12 +6966,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6964,11 +6984,6 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>0.000%</t>
@@ -6980,11 +6995,11 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>109</v>
+        <v>545361</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>441054</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -7004,7 +7019,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>SFMA-134393639</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7014,12 +7029,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7046,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -7046,35 +7061,35 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>453710</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>7015</v>
+        <v>5717</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>23371975</t>
+          <t>4557304</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7089,7 +7104,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>SFMA-134452674</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7099,12 +7114,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7116,12 +7131,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -7136,35 +7151,35 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>23.200%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>318742</t>
+          <t>177509947</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4146</v>
+        <v>545361</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>3983816</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>50.400%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-10.800%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7174,7 +7189,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>SFMA-134522369</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7184,12 +7199,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7201,55 +7216,55 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>16429</v>
+        <v>622</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>415386</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>75.000%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7259,7 +7274,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>SFMA-134532940</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7269,12 +7284,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7286,12 +7301,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7301,40 +7316,40 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.304%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>4059986</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>43</v>
+        <v>82769</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>30516879</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>70.800%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>-19.400%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7344,7 +7359,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>SFMA-134532940</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7354,12 +7369,12 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7371,12 +7386,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7386,40 +7401,40 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>1.002%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>30706</v>
+        <v>4148</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>1444547</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7429,7 +7444,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>SFMA-134532992</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7439,12 +7454,12 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7471,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>03/29/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7471,40 +7486,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.500%</t>
+          <t>-0.005%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>78752</t>
+          <t>-420</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>709</v>
+        <v>47994</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>5250114</t>
+          <t>7960381</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-5.100%</t>
+          <t>-13.000%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7514,7 +7529,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>GMMX-134404218</t>
+          <t>SFMA-134532992</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7524,12 +7539,12 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134404218/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7541,55 +7556,55 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>11/08/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>13.600%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-3.050%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>186601</t>
+          <t>-2489382</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1642</v>
+        <v>35300</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6547735</t>
+          <t>81620214</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>21.600%</t>
+          <t>36.200%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>-28.600%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7599,7 +7614,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>GMMX-134663952</t>
+          <t>SFMA-134532998</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7609,12 +7624,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134663952/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7641,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>06/23/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Encompass Indemnity Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7641,7 +7656,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7651,30 +7666,30 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.045%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-69278198</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>0</v>
+        <v>1152647</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>3761524</t>
+          <t>1712624141</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.700%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-43.600%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7684,7 +7699,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>GMMX-134490929</t>
+          <t>SFMA-134532998</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7694,12 +7709,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134490929/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7711,55 +7726,50 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>10/13/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Encompass Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>0.000%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-14.791%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-2798</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>5</v>
+        <v>545361</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>1256594719</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>11.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-23.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7769,7 +7779,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>GMMX-134694672</t>
+          <t>SFMA-134604280</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7779,12 +7789,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134694672/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7796,55 +7806,55 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.800%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11393108</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>91072</v>
+        <v>60097</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>116259930</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>38.000%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-8.300%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7854,7 +7864,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>SFMA-134620253</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7864,12 +7874,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7881,12 +7891,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7896,40 +7906,40 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2433030</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>25748</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19304787</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.900%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7939,7 +7949,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>SFMA-134620275</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7949,12 +7959,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7966,55 +7976,55 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>-8.959%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>-5629719</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>17719</v>
+        <v>29073</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>62836805</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-15.900%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8024,7 +8034,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>SFMA-134702926</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8034,12 +8044,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8051,55 +8061,55 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>-7.822%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>-130056850</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>54702</v>
+        <v>1174505</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>1662621165</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-12.200%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8109,7 +8119,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>SFMA-134702926</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8119,12 +8129,12 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8136,80 +8146,750 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>04/18/2026</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>15.700%</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0.001%</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>714</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>547530</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>1.900%</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-1.400%</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SFMA-134702973</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>15.700%</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>84036</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>35371108</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>0.100%</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-1.400%</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SFMA-134702973</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>State Farm Fire and Casualty Company</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0.005%</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>4641</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>1731791</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>1.400%</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>SFMA-134702979</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>12/15/2025</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>State Farm Mutual Automobile Insurance Company</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0.003%</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>48758</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>8319393</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>0.100%</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>SFMA-134702979</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>03/14/2025</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>12.800%</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>5.200%</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>9888509</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>45640</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>191265327</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>66.600%</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-28.800%</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>LBPM-134870677</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>output/pdfs/CO/134870677/filing_summary.pdf</t>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>20.700%</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>9.900%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>29899633</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>105836</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>302016491</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>21.400%</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-14.800%</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>TRVD-G134420284</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>05/17/2025</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>The Travelers Home and Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>28.800%</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>13.200%</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>5955691</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>15472</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>45118871</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>24.300%</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-2.900%</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>TRVD-G134450451</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>05/17/2025</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Travelers Commercial Insurance Company</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>28.800%</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>14.500%</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>244055</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>584</v>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>1683140</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>23.700%</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-2.500%</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>TRVD-G134450451</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>08/17/2025</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>106478</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>334013501</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>16.700%</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-35.000%</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>TRVD-G134585304</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>11/16/2025</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>100997</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>334013501</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>TRVD-G134688466</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4195,11 +4195,11 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>441054</t>
+          <t>202243</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>LBPM-134358341</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134358341/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4246,22 +4246,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>02/17/2025</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4280,11 +4280,11 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>7015</v>
+        <v>42196</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>23371975</t>
+          <t>146971869</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>LBPM-134358341</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4314,12 +4314,12 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134358341/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4365,11 +4365,11 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>441054</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4399,12 +4399,12 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>01/23/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4450,11 +4450,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>6706</v>
+        <v>7015</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>10503181</t>
+          <t>23371975</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134362517</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>186641</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4586,55 +4586,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>30706</v>
+        <v>6706</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>10503181</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4681,45 +4681,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>3.030%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>520683</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4756,55 +4756,55 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3.040%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>846342</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>8442</v>
+        <v>30706</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>27858972</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4866,30 +4866,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3.390%</t>
+          <t>3.030%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>515</v>
+        <v>121</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>3885888</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>8.130%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2.760%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LBPM-134814588</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Peerless Indemnity Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4951,30 +4951,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>3.040%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>318742</t>
+          <t>846342</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4146</v>
+        <v>8442</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>3983816</t>
+          <t>27858972</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>3.300%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>2.400%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5011,12 +5011,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5036,30 +5036,30 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>3.390%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>16429</v>
+        <v>515</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>3885888</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>8.130%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>2.760%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>LBPM-134814588</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5096,55 +5096,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>-66805</t>
+          <t>318742</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>596</v>
+        <v>4146</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1590594</t>
+          <t>3983816</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-14.930%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5181,55 +5181,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>-7.390%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>-22357214</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>345517</v>
+        <v>16429</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>745240469</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>25.060%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>-15.970%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-6.100%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-18329542</t>
+          <t>-66805</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>117383</v>
+        <v>596</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>300484287</t>
+          <t>1590594</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>22.510%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-25.160%</t>
+          <t>-14.930%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-7.390%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-28973</t>
+          <t>-22357214</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>226</v>
+        <v>345517</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>658471</t>
+          <t>745240469</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>8.180%</t>
+          <t>25.060%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-12.990%</t>
+          <t>-15.970%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5461,30 +5461,30 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>-6.100%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-13851</t>
+          <t>-18329542</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>218</v>
+        <v>117383</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>300484287</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>8.720%</t>
+          <t>22.510%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-9.440%</t>
+          <t>-25.160%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5541,35 +5541,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-116057</t>
+          <t>-28973</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>583</v>
+        <v>226</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>1589822</t>
+          <t>658471</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>-2.210%</t>
+          <t>8.180%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-9.680%</t>
+          <t>-12.990%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5626,35 +5626,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-22756464</t>
+          <t>-13851</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>120629</v>
+        <v>218</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>334653880</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>-1.290%</t>
+          <t>8.720%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-10.750%</t>
+          <t>-9.440%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5716,30 +5716,30 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-7.200%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-48359</t>
+          <t>-116057</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>225</v>
+        <v>583</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>671657</t>
+          <t>1589822</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-2.120%</t>
+          <t>-2.210%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-8.890%</t>
+          <t>-9.680%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5801,30 +5801,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-35656</t>
+          <t>-22756464</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>214</v>
+        <v>120629</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>334653880</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-2.760%</t>
+          <t>-1.290%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-9.790%</t>
+          <t>-10.750%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5881,35 +5881,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-7.050%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-4.800%</t>
+          <t>-7.200%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-35046584</t>
+          <t>-48359</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>354385</v>
+        <v>225</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>730137175</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>-2.120%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-8.560%</t>
+          <t>-8.890%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5946,55 +5946,55 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>American Economy Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>49.300%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>36.000%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>6297755</t>
+          <t>-35656</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>17719</v>
+        <v>214</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>17506322</t>
+          <t>488445</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>75.300%</t>
+          <t>-2.760%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-9.790%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6031,55 +6031,55 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>-7.050%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>-4.800%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>-35046584</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>54702</v>
+        <v>354385</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>730137175</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-8.560%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6131,40 +6131,40 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28040694</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>54702</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207965553</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>72.400%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-33.200%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6211,17 +6211,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6235,21 +6235,21 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>91072</v>
+        <v>0</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>LBPM-134450061</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6286,12 +6286,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6320,21 +6320,21 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>40568</v>
+        <v>91072</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96780298</t>
+          <t>310820277</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>SFMA-134294866</t>
+          <t>LBPM-134762479</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6405,21 +6405,21 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>1135697</v>
+        <v>40568</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1696535022</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>35.800%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-30.200%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6486,25 +6486,25 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4164</v>
+        <v>1135697</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1513879</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>35.800%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-8.900%</t>
+          <t>-30.200%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>SFMA-134320521</t>
+          <t>SFMA-134294866</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6566,30 +6566,30 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>-0.004%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>48376</v>
+        <v>4164</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>8064746</t>
+          <t>1513879</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-10.500%</t>
+          <t>-8.900%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6641,40 +6641,40 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-0.035%</t>
+          <t>-0.004%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-33639</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>40568</v>
+        <v>48376</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96780298</t>
+          <t>8064746</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>12.100%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-26.600%</t>
+          <t>-10.500%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>SFMA-134320536</t>
+          <t>SFMA-134320521</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6731,35 +6731,35 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0.200%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-0.013%</t>
+          <t>-0.035%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-213146</t>
+          <t>-33639</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1135697</v>
+        <v>40568</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>1696535022</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>12.100%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-21.700%</t>
+          <t>-26.600%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6811,40 +6811,40 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>0.001%</t>
+          <t>-0.013%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-213146</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>601</v>
+        <v>1135697</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>373240</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>-21.700%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134320543</t>
+          <t>SFMA-134320536</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6869,7 +6869,7 @@
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6886,7 +6886,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6906,30 +6906,30 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.001%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>-122</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>82673</v>
+        <v>601</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>30432911</t>
+          <t>373240</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6966,22 +6966,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6991,25 +6996,25 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-122</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>545361</v>
+        <v>82673</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>30432911</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7019,7 +7024,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134393639</t>
+          <t>SFMA-134320543</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7029,12 +7034,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7051,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7061,35 +7066,30 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>10.300%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>453710</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5717</v>
+        <v>545361</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>4557304</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134452674</t>
+          <t>SFMA-134393639</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -7146,40 +7146,40 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>23.200%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>16.400%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>177509947</t>
+          <t>453710</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>545361</v>
+        <v>5717</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>4557304</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>50.400%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>-10.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-134522369</t>
+          <t>SFMA-134452674</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7226,45 +7226,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>23.200%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>77260</t>
+          <t>177509947</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>622</v>
+        <v>545361</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>415386</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>75.000%</t>
+          <t>50.400%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-10.800%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-134532940</t>
+          <t>SFMA-134522369</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7326,30 +7326,30 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>13.304%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4059986</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>82769</v>
+        <v>622</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>30516879</t>
+          <t>415386</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>70.800%</t>
+          <t>75.000%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>-19.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7401,40 +7401,40 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>1.002%</t>
+          <t>13.304%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>4059986</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4148</v>
+        <v>82769</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>1444547</t>
+          <t>30516879</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>70.800%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-9.900%</t>
+          <t>-19.400%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-134532992</t>
+          <t>SFMA-134532940</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7496,20 +7496,20 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>-0.005%</t>
+          <t>1.002%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>-420</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>47994</v>
+        <v>4148</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>7960381</t>
+          <t>1444547</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-13.000%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7561,7 +7561,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7571,40 +7571,40 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>13.600%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-3.050%</t>
+          <t>-0.005%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-2489382</t>
+          <t>-420</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>35300</v>
+        <v>47994</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>81620214</t>
+          <t>7960381</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>36.200%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-28.600%</t>
+          <t>-13.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7614,7 +7614,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-134532998</t>
+          <t>SFMA-134532992</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -7661,35 +7661,35 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>13.600%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-4.045%</t>
+          <t>-3.050%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-69278198</t>
+          <t>-2489382</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1152647</v>
+        <v>35300</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1712624141</t>
+          <t>81620214</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>24.700%</t>
+          <t>36.200%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-43.600%</t>
+          <t>-28.600%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7726,50 +7726,55 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-4.045%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-69278198</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>545361</v>
+        <v>1152647</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1256594719</t>
+          <t>1712624141</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>24.700%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-43.600%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7779,7 +7784,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>SFMA-134604280</t>
+          <t>SFMA-134532998</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7789,12 +7794,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7806,7 +7811,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7821,40 +7826,35 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>11.000%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>9.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>11393108</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>60097</v>
+        <v>545361</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>116259930</t>
+          <t>1256594719</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>38.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>-8.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>SFMA-134620253</t>
+          <t>SFMA-134604280</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7911,35 +7911,35 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>9.800%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2433030</t>
+          <t>11393108</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>25748</v>
+        <v>60097</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>19304787</t>
+          <t>116259930</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>14.900%</t>
+          <t>38.000%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-8.300%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>SFMA-134620275</t>
+          <t>SFMA-134620253</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7986,45 +7986,45 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>-8.959%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>-5629719</t>
+          <t>2433030</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>29073</v>
+        <v>25748</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>62836805</t>
+          <t>19304787</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>14.900%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>-15.900%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>SFMA-134702926</t>
+          <t>SFMA-134620275</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8081,35 +8081,35 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-7.822%</t>
+          <t>-8.959%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-130056850</t>
+          <t>-5629719</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1174505</v>
+        <v>29073</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>1662621165</t>
+          <t>62836805</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-12.200%</t>
+          <t>-15.900%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8161,40 +8161,40 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>0.001%</t>
+          <t>-7.822%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-130056850</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>714</v>
+        <v>1174505</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>547530</t>
+          <t>1662621165</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>-12.200%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>SFMA-134702973</t>
+          <t>SFMA-134702926</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8256,25 +8256,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>0.001%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>84036</v>
+        <v>714</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>35371108</t>
+          <t>547530</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -8321,7 +8321,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -8331,40 +8331,40 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.005%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4641</v>
+        <v>84036</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1731791</t>
+          <t>35371108</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>0.100%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-1.400%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>SFMA-134702979</t>
+          <t>SFMA-134702973</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -8426,25 +8426,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.003%</t>
+          <t>0.005%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>48758</v>
+        <v>4641</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>8319393</t>
+          <t>1731791</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -8486,55 +8486,55 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>03/14/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>20.700%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.003%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>29899633</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>105836</v>
+        <v>48758</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>302016491</t>
+          <t>8319393</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>0.100%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>-14.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>TRVD-G134420284</t>
+          <t>SFMA-134702979</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8571,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>03/14/2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -8591,35 +8591,35 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>28.800%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>5955691</t>
+          <t>29899633</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>15472</v>
+        <v>105836</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>45118871</t>
+          <t>302016491</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>21.400%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>-14.800%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>TRVD-G134450451</t>
+          <t>TRVD-G134420284</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Travelers Commercial Insurance Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8681,30 +8681,30 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>14.500%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>244055</t>
+          <t>5955691</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>584</v>
+        <v>15472</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1683140</t>
+          <t>45118871</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>23.700%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-2.500%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>08/17/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Travelers Personal Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8759,32 +8759,37 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>28.800%</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>14.500%</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>244055</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>106478</v>
+        <v>584</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>334013501</t>
+          <t>1683140</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>16.700%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-35.000%</t>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -8794,7 +8799,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>TRVD-G134585304</t>
+          <t>TRVD-G134450451</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
@@ -8804,12 +8809,12 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2025-07-11</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8821,73 +8826,153 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
+          <t>08/17/2025</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Travelers Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>04.0 Homeowners</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>106478</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>334013501</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>16.700%</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-35.000%</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>TRVD-G134585304</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>11/16/2025</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>04.0 Homeowners</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="E101" t="inlineStr">
         <is>
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I100" t="n">
+      <c r="I101" t="n">
         <v>100997</v>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>334013501</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>TRVD-G134688466</t>
         </is>
       </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q101"/>
+  <dimension ref="A1:Q98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>01/23/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Insurance Company</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4450,11 +4450,11 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>7015</v>
+        <v>98</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>23371975</t>
+          <t>186641</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>LBPM-134362517</t>
+          <t>LBPM-134488149</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2025-01-09</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134362517/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4501,7 +4501,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4531,25 +4531,25 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>186641</t>
+          <t>89547</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.300%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -4559,7 +4559,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4586,55 +4586,55 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.200%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.000%</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2070653</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>6706</v>
+        <v>30706</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10503181</t>
+          <t>103250423</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>7.200%</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.500%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>LBPM-134488149</t>
+          <t>LBPM-134551958</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134488149/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4671,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>02/13/2026</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4681,45 +4681,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.030%</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>89547</t>
+          <t>520683</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-2.300%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134814553</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4739,12 +4739,12 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4756,55 +4756,55 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>03/20/2026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Liberty Mutual Fire Insurance Company</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-2.200%</t>
+          <t>15.400%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-2.000%</t>
+          <t>3.390%</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-2070653</t>
+          <t>131586</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>30706</v>
+        <v>515</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>103250423</t>
+          <t>3885888</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>7.200%</t>
+          <t>8.130%</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>-8.500%</t>
+          <t>2.760%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>LBPM-134551958</t>
+          <t>LBPM-134814588</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2025-05-29</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134551958/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance Company</t>
+          <t>Liberty Insurance Corporation</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4866,30 +4866,30 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>3.030%</t>
+          <t>8.000%</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>15791</t>
+          <t>318742</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>121</v>
+        <v>4146</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>520683</t>
+          <t>3983816</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>8.100%</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>4.400%</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Peerless Indemnity Insurance Company</t>
+          <t>Liberty Mutual Personal Insurance Company</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4951,30 +4951,30 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>3.040%</t>
+          <t>3.010%</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>846342</t>
+          <t>2486348</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8442</v>
+        <v>16429</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>27858972</t>
+          <t>82681536</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>3.300%</t>
+          <t>3.340%</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2.400%</t>
+          <t>2.100%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>LBPM-134814553</t>
+          <t>LBPM-134814602</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4999,7 +4999,7 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814553/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5011,55 +5011,55 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>03/20/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Liberty Mutual Fire Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.390%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>131586</t>
+          <t>-66805</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>515</v>
+        <v>596</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>3885888</t>
+          <t>1590594</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>8.130%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2.760%</t>
+          <t>-14.930%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>LBPM-134814588</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -5079,12 +5079,12 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814588/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5096,55 +5096,55 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Liberty Insurance Corporation</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-7.390%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>8.000%</t>
+          <t>-3.000%</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>318742</t>
+          <t>-22357214</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4146</v>
+        <v>345517</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>3983816</t>
+          <t>745240469</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>8.100%</t>
+          <t>25.060%</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>4.400%</t>
+          <t>-15.970%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -5164,12 +5164,12 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5181,55 +5181,55 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>02/13/2026</t>
+          <t>05/30/2025</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Liberty Mutual Personal Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>15.400%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3.010%</t>
+          <t>-6.100%</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2486348</t>
+          <t>-18329542</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>16429</v>
+        <v>117383</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>82681536</t>
+          <t>300484287</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>3.340%</t>
+          <t>22.510%</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2.100%</t>
+          <t>-25.160%</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>LBPM-134814602</t>
+          <t>PRGS-134483202</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -5249,12 +5249,12 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-05-30</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134814602/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5291,30 +5291,30 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-4.400%</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>-66805</t>
+          <t>-28973</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>596</v>
+        <v>226</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1590594</t>
+          <t>658471</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>8.180%</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>-14.930%</t>
+          <t>-12.990%</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5356,7 +5356,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5371,35 +5371,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-7.390%</t>
+          <t>-14.860%</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-3.000%</t>
+          <t>-4.000%</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>-22357214</t>
+          <t>-13851</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>345517</v>
+        <v>218</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>745240469</t>
+          <t>346283</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>25.060%</t>
+          <t>8.720%</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-15.970%</t>
+          <t>-9.440%</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -5436,12 +5436,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Casualty Insurance Company</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5456,35 +5456,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-6.100%</t>
+          <t>-7.300%</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>-18329542</t>
+          <t>-116057</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>117383</v>
+        <v>583</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>300484287</t>
+          <t>1589822</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22.510%</t>
+          <t>-2.210%</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>-25.160%</t>
+          <t>-9.680%</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5504,12 +5504,12 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5521,12 +5521,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Progressive Preferred Insurance Company</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5541,35 +5541,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-4.400%</t>
+          <t>-6.800%</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>-28973</t>
+          <t>-22756464</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>226</v>
+        <v>120629</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>658471</t>
+          <t>334653880</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>8.180%</t>
+          <t>-1.290%</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>-12.990%</t>
+          <t>-10.750%</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5606,12 +5606,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>05/30/2025</t>
+          <t>10/31/2025</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Progressive Specialty Insurance Company</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5626,35 +5626,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>-14.860%</t>
+          <t>-11.640%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-4.000%</t>
+          <t>-7.200%</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>-13851</t>
+          <t>-48359</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>346283</t>
+          <t>671657</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>8.720%</t>
+          <t>-2.120%</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>-9.440%</t>
+          <t>-8.890%</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>PRGS-134483202</t>
+          <t>PRGS-134710552</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134483202/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Progressive Casualty Insurance Company</t>
+          <t>Progressive Mountain Insurance Company</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5721,25 +5721,25 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>-116057</t>
+          <t>-35656</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>583</v>
+        <v>214</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1589822</t>
+          <t>488445</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>-2.210%</t>
+          <t>-2.760%</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>-9.680%</t>
+          <t>-9.790%</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Progressive Preferred Insurance Company</t>
+          <t>Progressive Direct Insurance Company</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5796,35 +5796,35 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>-7.050%</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>-6.800%</t>
+          <t>-4.800%</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>-22756464</t>
+          <t>-35046584</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>120629</v>
+        <v>354385</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>334653880</t>
+          <t>730137175</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>-1.290%</t>
+          <t>4.800%</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>-10.750%</t>
+          <t>-8.560%</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5861,55 +5861,55 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Progressive Specialty Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>17.100%</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>-7.200%</t>
+          <t>13.500%</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-48359</t>
+          <t>28040694</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>225</v>
+        <v>54702</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>671657</t>
+          <t>207965553</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>-2.120%</t>
+          <t>72.400%</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>-8.890%</t>
+          <t>-33.200%</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134412448</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-02-14</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -5946,55 +5946,55 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>04/14/2025</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Progressive Mountain Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>04.0001 Condominium Homeowners</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>-11.640%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>-7.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>-35656</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>214</v>
+        <v>0</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>488445</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-2.760%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-9.790%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134450061</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6031,12 +6031,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10/31/2025</t>
+          <t>02/15/2026</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Progressive Direct Insurance Company</t>
+          <t>Safeco Insurance Company of America</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6046,40 +6046,40 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-7.050%</t>
+          <t>3.000%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>-4.800%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>-35046584</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>354385</v>
+        <v>91072</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>730137175</t>
+          <t>310820277</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4.800%</t>
+          <t>21.000%</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-8.560%</t>
+          <t>-15.000%</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>PRGS-134710552</t>
+          <t>LBPM-134762479</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134710552/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6116,55 +6116,55 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17.100%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>13.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>28040694</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>54702</v>
+        <v>40568</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>207965553</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>72.400%</t>
+          <t>23.900%</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-33.200%</t>
+          <t>-24.800%</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>LBPM-134412448</t>
+          <t>SFMA-134294866</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2025-02-14</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134412448/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6201,22 +6201,22 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>04/14/2025</t>
+          <t>04/15/2025</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>04.0001 Condominium Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6235,21 +6235,21 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>1135697</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>35.800%</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-30.200%</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>LBPM-134450061</t>
+          <t>SFMA-134294866</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134450061/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6286,12 +6286,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>02/15/2026</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Safeco Insurance Company of America</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3.000%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6316,25 +6316,25 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>91072</v>
+        <v>4164</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>310820277</t>
+          <t>1513879</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>21.000%</t>
+          <t>5.600%</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-15.000%</t>
+          <t>-8.900%</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>LBPM-134762479</t>
+          <t>SFMA-134320521</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6354,12 +6354,12 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134762479/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6371,12 +6371,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6386,40 +6386,40 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.004%</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-285</t>
         </is>
       </c>
       <c r="I71" t="n">
-        <v>40568</v>
+        <v>48376</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96780298</t>
+          <t>8064746</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>23.900%</t>
+          <t>4.600%</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-24.800%</t>
+          <t>-10.500%</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>SFMA-134294866</t>
+          <t>SFMA-134320521</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>04/15/2025</t>
+          <t>01/27/2025</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6476,35 +6476,35 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-3.300%</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.035%</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-33639</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1135697</v>
+        <v>40568</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>1696535022</t>
+          <t>96780298</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>35.800%</t>
+          <t>12.100%</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-30.200%</t>
+          <t>-26.600%</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>SFMA-134294866</t>
+          <t>SFMA-134320536</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2024-11-22</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134294866/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6556,40 +6556,40 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>0.200%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-0.013%</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-213146</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4164</v>
+        <v>1135697</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1513879</t>
+          <t>1696535022</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>5.600%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-8.900%</t>
+          <t>-21.700%</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>SFMA-134320521</t>
+          <t>SFMA-134320536</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6651,30 +6651,30 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>-0.004%</t>
+          <t>0.001%</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>-285</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>48376</v>
+        <v>601</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>8064746</t>
+          <t>373240</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>4.600%</t>
+          <t>1.800%</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-10.500%</t>
+          <t>-2.600%</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -6684,7 +6684,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>SFMA-134320521</t>
+          <t>SFMA-134320543</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6699,7 +6699,7 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320521/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6726,40 +6726,40 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>-3.300%</t>
+          <t>3.700%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>-0.035%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>-33639</t>
+          <t>-122</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>40568</v>
+        <v>82673</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>96780298</t>
+          <t>30432911</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>12.100%</t>
+          <t>3.200%</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-26.600%</t>
+          <t>-4.200%</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -6769,7 +6769,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>SFMA-134320536</t>
+          <t>SFMA-134320543</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6796,55 +6796,50 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>03/15/2025</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>0.200%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>-0.013%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>-213146</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1135697</v>
+        <v>545361</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1696535022</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-21.700%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -6854,7 +6849,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>SFMA-134320536</t>
+          <t>SFMA-134393639</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6864,12 +6859,12 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320536/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6881,7 +6876,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>05/15/2025</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -6891,45 +6886,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0002 Mobile Homeowners</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>10.300%</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>0.001%</t>
+          <t>10.000%</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>453710</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>601</v>
+        <v>5717</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>373240</t>
+          <t>4557304</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>1.800%</t>
+          <t>11.200%</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>-2.600%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -6939,7 +6934,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>SFMA-134320543</t>
+          <t>SFMA-134452674</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6949,12 +6944,12 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -6966,55 +6961,55 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>01/27/2025</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>3.700%</t>
+          <t>23.200%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>16.400%</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>-122</t>
+          <t>177509947</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>82673</v>
+        <v>545361</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>30432911</t>
+          <t>1079084772</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>3.200%</t>
+          <t>50.400%</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>-4.200%</t>
+          <t>-10.800%</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -7024,7 +7019,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>SFMA-134320543</t>
+          <t>SFMA-134522369</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -7034,12 +7029,12 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2024-11-22</t>
+          <t>2025-05-09</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134320543/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7046,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>03/15/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -7061,35 +7056,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>18.600%</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>77260</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>545361</v>
+        <v>622</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>415386</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>75.000%</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>SFMA-134393639</t>
+          <t>SFMA-134532940</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -7114,12 +7114,12 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2025-02-07</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134393639/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7131,55 +7131,55 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>05/15/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>04.0002 Mobile Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>10.300%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>10.000%</t>
+          <t>13.304%</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>453710</t>
+          <t>4059986</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>5717</v>
+        <v>82769</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4557304</t>
+          <t>30516879</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>11.200%</t>
+          <t>70.800%</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-19.400%</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>SFMA-134452674</t>
+          <t>SFMA-134532940</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -7199,12 +7199,12 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134452674/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>07/01/2025</t>
+          <t>07/29/2025</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7226,45 +7226,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>23.200%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>16.400%</t>
+          <t>1.002%</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>177509947</t>
+          <t>14474</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>545361</v>
+        <v>4148</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1079084772</t>
+          <t>1444547</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>50.400%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>-10.800%</t>
+          <t>-9.900%</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>SFMA-134522369</t>
+          <t>SFMA-134532992</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7284,12 +7284,12 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2025-05-09</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134522369/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7316,40 +7316,40 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>18.600%</t>
+          <t>-0.005%</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>77260</t>
+          <t>-420</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>622</v>
+        <v>47994</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>415386</t>
+          <t>7960381</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>75.000%</t>
+          <t>35.300%</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-13.000%</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>SFMA-134532940</t>
+          <t>SFMA-134532992</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -7374,7 +7374,7 @@
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7401,40 +7401,40 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>13.600%</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>13.304%</t>
+          <t>-3.050%</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4059986</t>
+          <t>-2489382</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>82769</v>
+        <v>35300</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>30516879</t>
+          <t>81620214</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>70.800%</t>
+          <t>36.200%</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>-19.400%</t>
+          <t>-28.600%</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>SFMA-134532940</t>
+          <t>SFMA-134532998</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532940/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7476,7 +7476,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7486,40 +7486,40 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>19.0000 Personal Auto Combinations</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>1.002%</t>
+          <t>-4.045%</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>14474</t>
+          <t>-69278198</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4148</v>
+        <v>1152647</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>1444547</t>
+          <t>1712624141</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>24.700%</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>-9.900%</t>
+          <t>-43.600%</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>SFMA-134532992</t>
+          <t>SFMA-134532998</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7556,55 +7556,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>09/15/2025</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2.500%</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>-0.005%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>-420</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>47994</v>
+        <v>545361</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>7960381</t>
+          <t>1256594719</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>35.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>-13.000%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -7614,7 +7609,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>SFMA-134532992</t>
+          <t>SFMA-134604280</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7624,12 +7619,12 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532992/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7641,7 +7636,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -7651,45 +7646,45 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>13.600%</t>
+          <t>11.000%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>-3.050%</t>
+          <t>9.800%</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>-2489382</t>
+          <t>11393108</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>35300</v>
+        <v>60097</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>81620214</t>
+          <t>116259930</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>36.200%</t>
+          <t>38.000%</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>-28.600%</t>
+          <t>-8.300%</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
@@ -7699,7 +7694,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>SFMA-134532998</t>
+          <t>SFMA-134620253</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
@@ -7709,12 +7704,12 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7726,55 +7721,55 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>07/29/2025</t>
+          <t>10/15/2025</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>19.0000 Personal Auto Combinations</t>
+          <t>04.0005 Other Homeowners</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>25.800%</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>-4.045%</t>
+          <t>12.600%</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>-69278198</t>
+          <t>2433030</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1152647</v>
+        <v>25748</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>1712624141</t>
+          <t>19304787</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>24.700%</t>
+          <t>14.900%</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>-43.600%</t>
+          <t>2.800%</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -7784,7 +7779,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>SFMA-134532998</t>
+          <t>SFMA-134620275</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
@@ -7794,12 +7789,12 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134532998/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7811,7 +7806,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>09/15/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -7821,40 +7816,45 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>9.200%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-8.959%</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-5629719</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>545361</v>
+        <v>29073</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1256594719</t>
+          <t>62836805</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-15.900%</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>SFMA-134604280</t>
+          <t>SFMA-134702926</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7874,12 +7874,12 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134604280/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7891,55 +7891,55 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>11.000%</t>
+          <t>0.300%</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>9.800%</t>
+          <t>-7.822%</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>11393108</t>
+          <t>-130056850</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>60097</v>
+        <v>1174505</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>116259930</t>
+          <t>1662621165</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>38.000%</t>
+          <t>1.100%</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>-8.300%</t>
+          <t>-12.200%</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7949,7 +7949,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>SFMA-134620253</t>
+          <t>SFMA-134702926</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
@@ -7959,12 +7959,12 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620253/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>10/15/2025</t>
+          <t>12/15/2025</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -7986,45 +7986,45 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>04.0 Homeowners</t>
+          <t>19.0 Personal Auto</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>04.0005 Other Homeowners</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>25.800%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>12.600%</t>
+          <t>0.001%</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2433030</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>25748</v>
+        <v>714</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>19304787</t>
+          <t>547530</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>14.900%</t>
+          <t>1.900%</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>2.800%</t>
+          <t>-1.400%</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>SFMA-134620275</t>
+          <t>SFMA-134702973</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -8044,12 +8044,12 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134620275/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8066,7 +8066,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -8076,40 +8076,40 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0003 Recreational Vehicle (RV)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>9.200%</t>
+          <t>15.700%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>-8.959%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>-5629719</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>29073</v>
+        <v>84036</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>62836805</t>
+          <t>35371108</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>0.100%</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-15.900%</t>
+          <t>-1.400%</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>SFMA-134702926</t>
+          <t>SFMA-134702973</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>State Farm Fire and Casualty Company</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -8161,40 +8161,40 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>19.0001 Private Passenger Auto (PPA)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0.300%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-7.822%</t>
+          <t>0.005%</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>-130056850</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>1174505</v>
+        <v>4641</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>1662621165</t>
+          <t>1731791</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1.100%</t>
+          <t>1.400%</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>-12.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>SFMA-134702926</t>
+          <t>SFMA-134702979</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702926/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>State Farm Mutual Automobile Insurance Company</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -8246,40 +8246,40 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>19.0002 Motorcycle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>2.500%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>0.001%</t>
+          <t>0.003%</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>210</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>714</v>
+        <v>48758</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>547530</t>
+          <t>8319393</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>1.900%</t>
+          <t>0.100%</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>SFMA-134702973</t>
+          <t>SFMA-134702979</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8316,55 +8316,55 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>03/14/2025</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19.0003 Recreational Vehicle (RV)</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>15.700%</t>
+          <t>20.700%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>9.900%</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29899633</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>84036</v>
+        <v>105836</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>35371108</t>
+          <t>302016491</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>21.400%</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>-1.400%</t>
+          <t>-14.800%</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>SFMA-134702973</t>
+          <t>TRVD-G134420284</t>
         </is>
       </c>
       <c r="O94" t="inlineStr">
@@ -8384,12 +8384,12 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702973/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8401,55 +8401,55 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>State Farm Fire and Casualty Company</t>
+          <t>The Travelers Home and Marine Insurance Company</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>28.800%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>0.005%</t>
+          <t>13.200%</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>5955691</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4641</v>
+        <v>15472</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1731791</t>
+          <t>45118871</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1.400%</t>
+          <t>24.300%</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.900%</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -8459,7 +8459,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>SFMA-134702979</t>
+          <t>TRVD-G134450451</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8469,12 +8469,12 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8486,55 +8486,55 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>12/15/2025</t>
+          <t>05/17/2025</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>State Farm Mutual Automobile Insurance Company</t>
+          <t>Travelers Commercial Insurance Company</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>19.0 Personal Auto</t>
+          <t>04.0 Homeowners</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>19.0002 Motorcycle</t>
+          <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2.500%</t>
+          <t>28.800%</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>0.003%</t>
+          <t>14.500%</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>244055</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>48758</v>
+        <v>584</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>8319393</t>
+          <t>1683140</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>0.100%</t>
+          <t>23.700%</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>0.000%</t>
+          <t>-2.500%</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>SFMA-134702979</t>
+          <t>TRVD-G134450451</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134702979/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>03/14/2025</t>
+          <t>08/17/2025</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8589,37 +8589,32 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>20.700%</t>
-        </is>
-      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>9.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>29899633</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>105836</v>
+        <v>106478</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>302016491</t>
+          <t>334013501</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>21.400%</t>
+          <t>16.700%</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>-14.800%</t>
+          <t>-35.000%</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
@@ -8629,7 +8624,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>TRVD-G134420284</t>
+          <t>TRVD-G134585304</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
@@ -8639,12 +8634,12 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-07-11</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>output/pdfs/CO/134438849/filing_summary.pdf</t>
+          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
         </is>
       </c>
     </row>
@@ -8656,12 +8651,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>05/17/2025</t>
+          <t>11/16/2025</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>The Travelers Home and Marine Insurance Company</t>
+          <t>Travelers Personal Insurance Company</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8674,37 +8669,32 @@
           <t>04.0000 Homeowners Sub-TOI Combinations</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>28.800%</t>
-        </is>
-      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>13.200%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>5955691</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>15472</v>
+        <v>100997</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>45118871</t>
+          <t>334013501</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>24.300%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-2.900%</t>
+          <t>0.000%</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8714,7 +8704,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>TRVD-G134450451</t>
+          <t>TRVD-G134688466</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
@@ -8724,255 +8714,10 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
-        <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>05/17/2025</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Travelers Commercial Insurance Company</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>28.800%</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>14.500%</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>244055</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>584</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>1683140</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>23.700%</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>-2.500%</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>TRVD-G134450451</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P99" t="inlineStr">
-        <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Q99" t="inlineStr">
-        <is>
-          <t>output/pdfs/CO/134451532/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>08/17/2025</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Travelers Personal Insurance Company</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>106478</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>334013501</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>16.700%</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>-35.000%</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>TRVD-G134585304</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P100" t="inlineStr">
-        <is>
-          <t>2025-07-11</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>output/pdfs/CO/134602353/filing_summary.pdf</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>CO</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>11/16/2025</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Travelers Personal Insurance Company</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>04.0 Homeowners</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>04.0000 Homeowners Sub-TOI Combinations</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>100997</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>334013501</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>0.000%</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>rate_change</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>TRVD-G134688466</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>Filed</t>
-        </is>
-      </c>
-      <c r="P101" t="inlineStr">
-        <is>
-          <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="Q101" t="inlineStr">
         <is>
           <t>output/pdfs/CO/134700105/filing_summary.pdf</t>
         </is>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R192"/>
+  <dimension ref="A1:T192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,16 @@
           <t>validation_tier</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>external_validation</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -597,6 +607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -687,6 +707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -867,6 +907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -957,6 +1007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1047,6 +1107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1137,6 +1207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1227,6 +1307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1317,6 +1407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1407,6 +1507,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1497,6 +1607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1587,6 +1707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1677,6 +1807,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1767,6 +1907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1857,6 +2007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1947,6 +2107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2037,6 +2207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2127,6 +2307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2214,7 +2404,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2504,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2397,6 +2607,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2487,6 +2707,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2574,7 +2804,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -2667,6 +2907,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2757,6 +3007,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2847,6 +3107,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2937,6 +3207,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3027,6 +3307,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3117,6 +3407,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3204,7 +3504,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3604,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3704,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3474,7 +3804,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3904,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3654,7 +4004,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3744,7 +4104,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3834,7 +4204,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -3924,7 +4304,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4014,7 +4404,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4504,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4599,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4699,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4799,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4899,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4999,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4639,7 +5099,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4729,7 +5199,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -4822,6 +5302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4912,6 +5402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5002,6 +5502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5092,6 +5602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5182,6 +5702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5269,7 +5799,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5359,7 +5899,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5999,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5539,7 +6099,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -5632,6 +6202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5722,6 +6302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5812,6 +6402,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5902,6 +6502,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5992,6 +6602,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6082,6 +6702,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6172,6 +6802,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6262,6 +6902,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -6352,6 +7002,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -6442,6 +7102,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6532,6 +7202,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6622,6 +7302,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6707,6 +7397,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6792,6 +7492,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6877,6 +7587,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6962,6 +7682,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7047,6 +7777,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7134,7 +7874,17 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7974,17 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7314,7 +8074,17 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7404,7 +8174,17 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7494,7 +8274,17 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7584,7 +8374,17 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7674,7 +8474,17 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7764,7 +8574,17 @@
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7854,7 +8674,17 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -7944,7 +8774,17 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8034,7 +8874,17 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8124,7 +8974,17 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8214,7 +9074,17 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8304,7 +9174,17 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8394,7 +9274,17 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8484,7 +9374,17 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8574,7 +9474,17 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8664,7 +9574,17 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -8757,6 +9677,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -8847,6 +9777,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -8937,6 +9877,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9027,6 +9977,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -9117,6 +10077,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -9207,6 +10177,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -9297,6 +10277,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -9387,6 +10377,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -9477,6 +10477,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -9567,6 +10577,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -9657,6 +10677,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -9744,7 +10774,17 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9834,7 +10874,17 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -9924,7 +10974,17 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10014,7 +11074,17 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10104,7 +11174,17 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10194,7 +11274,17 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10284,7 +11374,17 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10374,7 +11474,17 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10464,7 +11574,17 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10554,7 +11674,17 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -10647,6 +11777,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -10737,6 +11877,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -10827,6 +11977,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -10917,6 +12077,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -11007,6 +12177,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -11097,6 +12277,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -11187,6 +12377,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -11277,6 +12477,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -11367,6 +12577,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -11457,6 +12677,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -11547,6 +12777,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -11634,7 +12874,17 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11724,7 +12974,17 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11814,7 +13074,17 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11904,7 +13174,17 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -11994,7 +13274,17 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12084,7 +13374,17 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12174,7 +13474,17 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12264,7 +13574,17 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12354,7 +13674,17 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12444,7 +13774,17 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12537,6 +13877,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -12627,6 +13977,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -12714,7 +14074,17 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12804,7 +14174,17 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12894,7 +14274,17 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -12987,6 +14377,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -13077,6 +14477,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -13162,6 +14572,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -13252,6 +14672,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -13342,6 +14772,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -13432,6 +14872,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -13522,6 +14972,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -13612,6 +15072,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -13702,6 +15172,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -13792,6 +15272,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -13882,6 +15372,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -13972,6 +15472,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -14062,6 +15572,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -14152,6 +15672,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -14242,6 +15772,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -14332,6 +15872,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -14419,7 +15969,17 @@
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14509,7 +16069,17 @@
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14599,7 +16169,17 @@
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14689,7 +16269,17 @@
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14779,7 +16369,17 @@
       </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14869,7 +16469,17 @@
       </c>
       <c r="R161" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -14959,7 +16569,17 @@
       </c>
       <c r="R162" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15049,7 +16669,17 @@
       </c>
       <c r="R163" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15134,7 +16764,17 @@
       </c>
       <c r="R164" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15224,7 +16864,17 @@
       </c>
       <c r="R165" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15314,7 +16964,17 @@
       </c>
       <c r="R166" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15404,7 +17064,17 @@
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15494,7 +17164,17 @@
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15584,7 +17264,17 @@
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15674,7 +17364,17 @@
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15764,7 +17464,17 @@
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15854,7 +17564,17 @@
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -15939,7 +17659,17 @@
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16029,7 +17759,17 @@
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16119,7 +17859,17 @@
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16209,7 +17959,17 @@
       </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16299,7 +18059,17 @@
       </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16389,7 +18159,17 @@
       </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16479,7 +18259,17 @@
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16569,7 +18359,17 @@
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16659,7 +18459,17 @@
       </c>
       <c r="R181" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -16752,6 +18562,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -16842,6 +18662,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -16932,6 +18762,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -17017,6 +18857,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -17102,6 +18952,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -17187,6 +19047,16 @@
           <t>pipeline_only</t>
         </is>
       </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>extension</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -17274,7 +19144,17 @@
       </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -17364,7 +19244,17 @@
       </c>
       <c r="R189" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -17454,7 +19344,17 @@
       </c>
       <c r="R190" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -17539,7 +19439,17 @@
       </c>
       <c r="R191" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>
@@ -17624,7 +19534,17 @@
       </c>
       <c r="R192" t="inlineStr">
         <is>
-          <t>ambest_validated</t>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>unvalidated</t>
         </is>
       </c>
     </row>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T192"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,11 @@
           <t>external_validation</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>match_strength</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -614,9 +619,10 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -714,9 +720,10 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -814,9 +821,10 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -914,9 +922,10 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1014,9 +1023,10 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1114,9 +1124,10 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1214,9 +1225,10 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1314,9 +1326,10 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1414,9 +1427,10 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1514,9 +1528,10 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1614,9 +1629,10 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1714,9 +1730,10 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1814,9 +1831,10 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1914,9 +1932,10 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2014,9 +2033,10 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2114,9 +2134,10 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2214,9 +2235,10 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2314,9 +2336,10 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2414,9 +2437,10 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2514,9 +2538,10 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2614,9 +2639,10 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2714,9 +2740,10 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2814,9 +2841,10 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2914,9 +2942,10 @@
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3014,9 +3043,10 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3114,9 +3144,10 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3214,9 +3245,10 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3314,9 +3346,10 @@
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3414,9 +3447,10 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3514,9 +3548,10 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3614,9 +3649,10 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3714,9 +3750,10 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3814,9 +3851,10 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3914,9 +3952,10 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4014,9 +4053,10 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4114,9 +4154,10 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4214,9 +4255,10 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4314,9 +4356,10 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4414,9 +4457,10 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4514,9 +4558,10 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4609,9 +4654,10 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4709,9 +4755,10 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4809,9 +4856,10 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4909,9 +4957,10 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5009,9 +5058,10 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5109,9 +5159,10 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5209,9 +5260,10 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5309,9 +5361,10 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5409,9 +5462,10 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5509,9 +5563,10 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5609,9 +5664,10 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5709,9 +5765,10 @@
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5809,9 +5866,10 @@
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5909,9 +5967,10 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6009,9 +6068,10 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6109,9 +6169,10 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6209,9 +6270,10 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6309,9 +6371,10 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6409,9 +6472,10 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6509,9 +6573,10 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6609,9 +6674,10 @@
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6709,9 +6775,10 @@
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6809,9 +6876,10 @@
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -6909,9 +6977,10 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7009,9 +7078,10 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7109,9 +7179,10 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7209,9 +7280,10 @@
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7309,9 +7381,10 @@
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7404,9 +7477,10 @@
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7499,9 +7573,10 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7594,9 +7669,10 @@
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7689,9 +7765,10 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -7784,9 +7861,10 @@
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -7884,9 +7962,10 @@
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -7984,9 +8063,10 @@
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8084,9 +8164,10 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8184,9 +8265,10 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -8284,9 +8366,10 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -8384,9 +8467,10 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -8484,9 +8568,10 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -8584,9 +8669,10 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -8684,9 +8770,10 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -8784,9 +8871,10 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -8884,9 +8972,10 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -8984,9 +9073,10 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9084,9 +9174,10 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -9184,9 +9275,10 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -9284,9 +9376,10 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -9384,9 +9477,10 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -9484,9 +9578,10 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -9584,9 +9679,10 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -9684,9 +9780,10 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -9784,9 +9881,10 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -9884,9 +9982,10 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -9984,9 +10083,10 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -10084,9 +10184,10 @@
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -10184,9 +10285,10 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -10284,9 +10386,10 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -10384,9 +10487,10 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -10484,9 +10588,10 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -10584,9 +10689,10 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -10684,9 +10790,10 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -10784,9 +10891,10 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -10884,9 +10992,10 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -10984,9 +11093,10 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -11084,9 +11194,10 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -11184,9 +11295,10 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -11284,9 +11396,10 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -11384,9 +11497,10 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -11484,9 +11598,10 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -11584,9 +11699,10 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -11684,9 +11800,10 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -11784,9 +11901,10 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -11884,9 +12002,10 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -11984,9 +12103,10 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -12084,9 +12204,10 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -12184,9 +12305,10 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -12284,9 +12406,10 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -12384,9 +12507,10 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -12484,9 +12608,10 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -12584,9 +12709,10 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -12684,9 +12810,10 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -12784,9 +12911,10 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -12884,9 +13012,10 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -12984,9 +13113,10 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -13084,9 +13214,10 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -13184,9 +13315,10 @@
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -13284,9 +13416,10 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -13384,9 +13517,10 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -13484,9 +13618,10 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -13584,9 +13719,10 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -13684,9 +13820,10 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -13784,9 +13921,10 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -13884,9 +14022,10 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -13984,9 +14123,10 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -14084,9 +14224,10 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -14184,9 +14325,10 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -14284,9 +14426,10 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -14384,9 +14527,10 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -14484,9 +14628,10 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -14579,9 +14724,10 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -14679,9 +14825,10 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -14779,9 +14926,10 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -14879,9 +15027,10 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -14979,9 +15128,10 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -15079,9 +15229,10 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -15179,9 +15330,10 @@
       </c>
       <c r="T148" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -15279,9 +15431,10 @@
       </c>
       <c r="T149" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -15379,9 +15532,10 @@
       </c>
       <c r="T150" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -15479,9 +15633,10 @@
       </c>
       <c r="T151" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -15579,9 +15734,10 @@
       </c>
       <c r="T152" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -15679,9 +15835,10 @@
       </c>
       <c r="T153" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -15779,9 +15936,10 @@
       </c>
       <c r="T154" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -15879,9 +16037,10 @@
       </c>
       <c r="T155" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -15979,9 +16138,10 @@
       </c>
       <c r="T156" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -16079,9 +16239,10 @@
       </c>
       <c r="T157" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -16179,9 +16340,10 @@
       </c>
       <c r="T158" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -16279,9 +16441,10 @@
       </c>
       <c r="T159" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -16379,9 +16542,10 @@
       </c>
       <c r="T160" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -16479,9 +16643,10 @@
       </c>
       <c r="T161" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -16579,9 +16744,10 @@
       </c>
       <c r="T162" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -16679,9 +16845,10 @@
       </c>
       <c r="T163" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -16774,9 +16941,10 @@
       </c>
       <c r="T164" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -16874,9 +17042,10 @@
       </c>
       <c r="T165" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -16974,9 +17143,10 @@
       </c>
       <c r="T166" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -17074,9 +17244,10 @@
       </c>
       <c r="T167" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -17174,9 +17345,10 @@
       </c>
       <c r="T168" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -17274,9 +17446,10 @@
       </c>
       <c r="T169" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -17374,9 +17547,10 @@
       </c>
       <c r="T170" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -17474,9 +17648,10 @@
       </c>
       <c r="T171" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -17574,9 +17749,10 @@
       </c>
       <c r="T172" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -17669,9 +17845,10 @@
       </c>
       <c r="T173" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -17769,9 +17946,10 @@
       </c>
       <c r="T174" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -17869,9 +18047,10 @@
       </c>
       <c r="T175" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -17969,9 +18148,10 @@
       </c>
       <c r="T176" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -18069,9 +18249,10 @@
       </c>
       <c r="T177" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -18169,9 +18350,10 @@
       </c>
       <c r="T178" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -18269,9 +18451,10 @@
       </c>
       <c r="T179" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -18369,9 +18552,10 @@
       </c>
       <c r="T180" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -18469,9 +18653,10 @@
       </c>
       <c r="T181" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -18569,9 +18754,10 @@
       </c>
       <c r="T182" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -18669,9 +18855,10 @@
       </c>
       <c r="T183" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -18769,9 +18956,10 @@
       </c>
       <c r="T184" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -18864,9 +19052,10 @@
       </c>
       <c r="T185" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -18959,9 +19148,10 @@
       </c>
       <c r="T186" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -19054,9 +19244,10 @@
       </c>
       <c r="T187" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -19154,9 +19345,10 @@
       </c>
       <c r="T188" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -19254,9 +19446,10 @@
       </c>
       <c r="T189" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -19354,9 +19547,10 @@
       </c>
       <c r="T190" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -19449,9 +19643,10 @@
       </c>
       <c r="T191" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -19544,9 +19739,10 @@
       </c>
       <c r="T192" t="inlineStr">
         <is>
-          <t>unvalidated</t>
-        </is>
-      </c>
+          <t>pipeline_extracted</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Insurance Rate Data Scraper/output/co_final_rates.xlsx
+++ b/Insurance Rate Data Scraper/output/co_final_rates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U205"/>
+  <dimension ref="A1:U223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21051,6 +21051,1724 @@
         </is>
       </c>
       <c r="U205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>GEICO Advantage Insurance Company</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-6.300%</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-4.700%</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>-1231252</t>
+        </is>
+      </c>
+      <c r="I206" t="n">
+        <v>21550</v>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>26386477</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>5.990%</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-11.480%</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>GECC-134903984</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134903984/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>04/24/2026</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>GEICO Marine Insurance Company</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-6.300%</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-4.900%</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>-534668</t>
+        </is>
+      </c>
+      <c r="I207" t="n">
+        <v>6147</v>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>10813411</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>9.030%</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-10.190%</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>GECC-134903984</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134903984/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>GEICO Choice Insurance Company</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>GECC-134908723</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134908723/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>GEICO Secure Insurance Company</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>GECC-134908723</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134908723/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>06/15/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Allstate Fire and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>417513467</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ALSE-134915581</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134915581/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>LBPM-134929227</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134929227/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Fire Insurance Company</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2.200%</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>37083</t>
+        </is>
+      </c>
+      <c r="I212" t="n">
+        <v>281</v>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>1664993</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>15.400%</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-3.400%</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>LBPM-134929227</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134929227/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>The First Liberty Insurance Corporation</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>4.100%</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>2666</t>
+        </is>
+      </c>
+      <c r="I213" t="n">
+        <v>13</v>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>65174</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>12.700%</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>-1.900%</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>LBPM-134929227</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134929227/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Insurance Company</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-0.840%</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-608</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>32</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>72094</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>15.500%</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-26.000%</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>LBPM-134929216</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134929216/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>05/30/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Liberty Mutual Personal Insurance Company</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>19.0000 Personal Auto Combinations</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2.500%</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2.290%</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>2163448</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>28990</v>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>94274388</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>24.100%</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>-55.000%</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>LBPM-134929216</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134929216/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>07/01/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Safeco Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>19.0004 Other</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>54.300%</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>11.005%</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>98339</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>3779</v>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>893556</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>54.300%</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>LBPM-134915617</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134915617/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>06/13/2026</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>General Insurance Company of America</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>19.0002 Motorcycle</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>10018</v>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>4598955</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>LBPM-134941507</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134941507/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>05/25/2026</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Encompass Insurance Company</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-2.090%</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-14451</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>218</v>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>691459</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>0.000%</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>-8.590%</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>GMMX-134954059</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134954059/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>05/07/2026</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Nationwide General Insurance Company</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>-12.300%</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>-10.000%</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-2058811</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>6131</v>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>20588106</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>5.300%</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>-29.300%</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>NWPP-G134892060</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134898637/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>United Services Automobile Association</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-14.700%</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-1.500%</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-3830326</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>66765</v>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>255355075</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-30.000%</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>USAA-134924660</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134924660/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>USAA Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>-20.000%</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>-1.000%</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>-3159732</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>92966</v>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>315973181</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-30.000%</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>USAA-134924660</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134924660/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>USAA General Indemnity Company</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>-10.100%</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>-3.000%</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-4310747</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>44140</v>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>143691578</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-30.000%</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>USAA-134924660</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134924660/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>CO</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>08/07/2026</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Garrison Property and Casualty Insurance Company</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>19.0 Personal Auto</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>19.0001 Private Passenger Auto (PPA)</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-14.100%</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-1.000%</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>-1440202</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>54228</v>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>144020176</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>5.000%</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-30.000%</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>rate_change</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>USAA-134924660</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Filed</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>output/pdfs/CO/134924660/filing_summary.pdf</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>pipeline_only</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>original</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>pipeline_extracted_in_validated_window</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
